--- a/expense_template_v3.xlsx
+++ b/expense_template_v3.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Form No. F-001-v3 / Governing policy: DL-HR-RG-2024-007 (Revision 3, revised October 1, 2024)</t>
+          <t>Form No. F-001-v3 / Governing policy: NL-HR-RG-2024-007 (Revision 3, revised October 1, 2024)</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>DL-04321</t>
+          <t>NL-04321</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Governing policy: Demo Logistics Inc. Travel, Expense Reimbursement and HR Procedures Policy (DL-HR-RG-2024-007, Revision 3)</t>
+          <t>Governing policy: Nexus Logistics, Inc. Travel, Expense Reimbursement and HR Procedures Policy (NL-HR-RG-2024-007, Revision 3)</t>
         </is>
       </c>
     </row>
@@ -2485,14 +2485,14 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Expenses and payments: Accounts Payable (ext. 1456 / accounts-payable@demo-logistics.example.com)</t>
+          <t>Expenses and payments: Accounts Payable (ext. 1456 / accounts-payable@nexus-logistics.example.com)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Policy and HR: People Operations (ext. 1234 / people-ops@demo-logistics.example.com)</t>
+          <t>Policy and HR: People Operations (ext. 1234 / people-ops@nexus-logistics.example.com)</t>
         </is>
       </c>
     </row>
